--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484677_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484677_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2132</v>
+        <v>5.09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4593</v>
+        <v>4.1131</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7539</v>
+        <v>0.9768</v>
       </c>
       <c r="G2" t="n">
         <v>1.1793</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>2.657</v>
+        <v>1.5338</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1041</v>
+        <v>0.7579</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5528</v>
+        <v>0.7758</v>
       </c>
       <c r="V2" t="n">
         <v>1.2774</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8669</v>
+        <v>3.0122</v>
       </c>
       <c r="E3" t="n">
-        <v>1.045</v>
+        <v>1.3885</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8219</v>
+        <v>1.6237</v>
       </c>
       <c r="G3" t="n">
         <v>0.499</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1243</v>
+        <v>0.2696</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.46</v>
+        <v>-0.1165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5843</v>
+        <v>0.3861</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3219</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6005</v>
+        <v>2.3294</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6005</v>
+        <v>0.1511</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2.1783</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6005</v>
+        <v>-5.2242</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9752999999999999</v>
+        <v>-2.7371</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6251</v>
+        <v>-2.4871</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6005</v>
+        <v>-2.1557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.5024</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6251</v>
+        <v>-1.6533</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-3.0685</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.2347</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.8338</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.2149</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.0485</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.3054</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.3539</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.1229</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.4448</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. PADILLA MARTINEZ</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5884</v>
+        <v>1.6005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5393</v>
+        <v>1.6005</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0491</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3397</v>
+        <v>1.6005</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8239</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4842</v>
+        <v>0.6251</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4878</v>
+        <v>1.6005</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1645</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6766</v>
+        <v>0.6251</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8519</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6594</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1925</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9281</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6765</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2517</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>S. PADILLA MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3494</v>
+        <v>1.5255</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2501</v>
+        <v>0.4021</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5995</v>
+        <v>1.1234</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.2242</v>
+        <v>-1.3397</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.7371</v>
+        <v>-1.8239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4871</v>
+        <v>0.4842</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1557</v>
+        <v>-0.4878</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5024</v>
+        <v>-1.1645</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6533</v>
+        <v>0.6766</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0685</v>
+        <v>-0.8519</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2347</v>
+        <v>-0.6594</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8338</v>
+        <v>-0.1925</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3823</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>4.2149</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0684</v>
+        <v>0.8652</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7066</v>
+        <v>0.5392</v>
       </c>
       <c r="U6" t="n">
-        <v>1.775</v>
+        <v>0.326</v>
       </c>
       <c r="V6" t="n">
-        <v>4.1229</v>
+        <v>1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>4.4448</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1969</v>
+        <v>1.175</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8641</v>
+        <v>0.7679</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3328</v>
+        <v>0.4071</v>
       </c>
       <c r="G7" t="n">
         <v>0.3676</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6906</v>
+        <v>0.6687</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3107</v>
+        <v>0.2146</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3799</v>
+        <v>0.4542</v>
       </c>
       <c r="V7" t="n">
         <v>0.3219</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6251</v>
+        <v>1.0553</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6251</v>
+        <v>-0.9718</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.0271</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6251</v>
+        <v>-1.4317</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-2.3042</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6251</v>
+        <v>0.2491</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.5852</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>-2.336</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.6808</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.7127</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.0318</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.2986</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.1046</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.4093</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3604</v>
+        <v>0.6251</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4708</v>
+        <v>0.6251</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1104</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2574</v>
+        <v>0.6251</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6542</v>
+        <v>0.6251</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1163</v>
+        <v>0.6251</v>
       </c>
       <c r="K10" t="n">
-        <v>2.065</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9487</v>
+        <v>0.6251</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3738</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6682</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7056</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.6651</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.0077</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5536</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4541</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>G. KRISHNAN SELVARAJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1843</v>
+        <v>-0.5085</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9884</v>
+        <v>-0.9163</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8041</v>
+        <v>0.4078</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4317</v>
+        <v>0.2564</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8725000000000001</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3042</v>
+        <v>0.2564</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2491</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5852</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.336</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6808</v>
+        <v>0.2564</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7127</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0318</v>
+        <v>0.2564</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3823</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2986</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1349</v>
+        <v>0.1514</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3212</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1863</v>
+        <v>0.1514</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. KRISHNAN SELVARAJ</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4342</v>
+        <v>-0.8984</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9163</v>
+        <v>0.5093</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4821</v>
+        <v>-1.4077</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2564</v>
+        <v>-2.2574</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2564</v>
+        <v>-1.6542</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.1163</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2.065</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.9487</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2564</v>
+        <v>-3.3738</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-2.6682</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2564</v>
+        <v>-0.7056</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.6651</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2257</v>
+        <v>1.7489</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.592</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2257</v>
+        <v>1.1568</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.817</v>
+        <v>-1.4457</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0794</v>
+        <v>-2.1289</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2624</v>
+        <v>0.6833</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3405</v>
+        <v>-3.2962</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4015</v>
+        <v>-3.5685</v>
       </c>
       <c r="I13" t="n">
-        <v>1.061</v>
+        <v>0.2723</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4884</v>
+        <v>-1.0871</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.22</v>
+        <v>-1.9047</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7085</v>
+        <v>0.8176</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.829</v>
+        <v>-2.2091</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1815</v>
+        <v>-1.6638</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3525</v>
+        <v>-0.5452</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8613</v>
+        <v>0.5677</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0973</v>
+        <v>-0.1255</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.236</v>
+        <v>0.6932</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.4845</v>
+        <v>-2.4043</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.9943</v>
+        <v>-2.8897</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5099</v>
+        <v>0.4854</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2962</v>
+        <v>-0.3405</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.5685</v>
+        <v>-1.4015</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2723</v>
+        <v>1.061</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0871</v>
+        <v>0.4884</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9047</v>
+        <v>-0.22</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8176</v>
+        <v>0.7085</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2091</v>
+        <v>-0.829</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6638</v>
+        <v>-1.1815</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5452</v>
+        <v>0.3525</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2828</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4711</v>
+        <v>0.274</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9909</v>
+        <v>0.287</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5198</v>
+        <v>-0.013</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="15">
@@ -1579,22 +1579,22 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.5059</v>
+        <v>11.7812</v>
       </c>
       <c r="E15" t="n">
-        <v>3.000700000000001</v>
+        <v>3.275999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>8.5053</v>
+        <v>8.5052</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.736699999999999</v>
+        <v>-8.736700000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.218800000000002</v>
+        <v>-9.2188</v>
       </c>
       <c r="I15" t="n">
-        <v>0.482</v>
+        <v>0.4820000000000004</v>
       </c>
       <c r="J15" t="n">
         <v>7.537000000000001</v>
@@ -1615,7 +1615,7 @@
         <v>-1.6048</v>
       </c>
       <c r="P15" t="n">
-        <v>9.162699999999997</v>
+        <v>9.162699999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-13.7444</v>
@@ -1624,16 +1624,16 @@
         <v>22.907</v>
       </c>
       <c r="S15" t="n">
-        <v>6.9571</v>
+        <v>7.2324</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2635</v>
+        <v>1.5387</v>
       </c>
       <c r="U15" t="n">
-        <v>5.6936</v>
+        <v>5.693700000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>4.123</v>
+        <v>4.122999999999998</v>
       </c>
       <c r="W15" t="n">
         <v>7.944599999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3202</v>
+        <v>2.2403</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0689</v>
+        <v>0.3379</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2512</v>
+        <v>1.9024</v>
       </c>
       <c r="G16" t="n">
-        <v>5.1557</v>
+        <v>2.7763</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1688</v>
+        <v>1.443</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9869</v>
+        <v>1.3333</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2371</v>
+        <v>1.3372</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7368</v>
+        <v>1.8949</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5003</v>
+        <v>-0.5577</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0814</v>
+        <v>1.4391</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.4519</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5134</v>
+        <v>1.891</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.9321</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.4977</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4081</v>
+        <v>-0.5805</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2594</v>
+        <v>-0.083</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6675</v>
+        <v>-0.4976</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3115</v>
+        <v>-0.3219</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9005</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7755</v>
+        <v>1.4459</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1456</v>
+        <v>1.492</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6298</v>
+        <v>-0.0461</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7763</v>
+        <v>5.1557</v>
       </c>
       <c r="H17" t="n">
-        <v>1.443</v>
+        <v>4.1688</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3333</v>
+        <v>0.9869</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3372</v>
+        <v>6.2371</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8949</v>
+        <v>4.7368</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5577</v>
+        <v>1.5003</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4391</v>
+        <v>-1.0814</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4519</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>1.891</v>
+        <v>-0.5134</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-5.4977</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0453</v>
+        <v>-0.4661</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2753</v>
+        <v>-0.8363</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7701</v>
+        <v>0.3702</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3629</v>
+        <v>0.0725</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1738</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5367</v>
+        <v>-0.0119</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6907</v>
+        <v>-0.2619</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1493</v>
+        <v>-0.3901</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4586</v>
+        <v>0.1282</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3158</v>
+        <v>0.0433</v>
       </c>
       <c r="K18" t="n">
-        <v>4.0623</v>
+        <v>0.0433</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7465</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.625</v>
+        <v>-0.3053</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.913</v>
+        <v>-0.4335</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2879</v>
+        <v>0.1282</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5656</v>
+        <v>0.1833</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2282</v>
+        <v>0.1512</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7353</v>
+        <v>0.0411</v>
       </c>
       <c r="U18" t="n">
-        <v>0.507</v>
+        <v>0.1101</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0755</v>
+        <v>-0.4239</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0117</v>
+        <v>-0.3661</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0872</v>
+        <v>-0.0578</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2619</v>
+        <v>1.6907</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3901</v>
+        <v>3.1493</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1282</v>
+        <v>-1.4586</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0433</v>
+        <v>2.3158</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0433</v>
+        <v>4.0623</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.7465</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3053</v>
+        <v>-0.625</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4335</v>
+        <v>-0.913</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1282</v>
+        <v>0.2879</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1833</v>
+        <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1541</v>
+        <v>-1.0151</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0551</v>
+        <v>-0.9276</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2092</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3659</v>
+        <v>-1.7553</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5718</v>
+        <v>-1.2833</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7941</v>
+        <v>-0.472</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3061</v>
@@ -2014,13 +2014,13 @@
         <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0756</v>
+        <v>-1.4651</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.101</v>
+        <v>-0.8126</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9746</v>
+        <v>-0.6526</v>
       </c>
       <c r="V20" t="n">
         <v>-1.267</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.576</v>
+        <v>-3.2074</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4945</v>
+        <v>-3.3983</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0815</v>
+        <v>0.191</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9245</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.175</v>
+        <v>-0.8064</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9909</v>
+        <v>-0.8948</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1841</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0.6231</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.787</v>
+        <v>-4.452</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6696</v>
+        <v>-4.285</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1174</v>
+        <v>-0.1669</v>
       </c>
       <c r="G22" t="n">
         <v>1.6502</v>
@@ -2170,13 +2170,13 @@
         <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7721</v>
+        <v>-1.437</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5414</v>
+        <v>-1.1568</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2307</v>
+        <v>-0.2802</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3111</v>
+        <v>-5.4261</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7984</v>
+        <v>-1.0869</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5126</v>
+        <v>-4.3392</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0435</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.223</v>
+        <v>-1.338</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7353</v>
+        <v>-1.0237</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4877</v>
+        <v>-0.3143</v>
       </c>
       <c r="V23" t="n">
         <v>-2.212</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.5059</v>
+        <v>-11.506</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.5053</v>
+        <v>-8.5052</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.000700000000001</v>
+        <v>-3.0005</v>
       </c>
       <c r="G24" t="n">
         <v>8.7369</v>
